--- a/docs/d/06/inyear.xlsx
+++ b/docs/d/06/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 91 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 89 clubs short</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>1</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8583,8 +8583,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="P94" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q94" s="9" t="n">
         <v>0</v>
@@ -11100,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T104" s="10" t="n">
         <v>1</v>
@@ -17847,7 +17847,7 @@
         <v>0</v>
       </c>
       <c r="S171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T171" s="9" t="n">
         <v>0</v>
@@ -18811,7 +18811,7 @@
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -18881,8 +18881,8 @@
       <c r="Y181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z181" s="9" t="n">
-        <v>0</v>
+      <c r="Z181" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA181" s="10" t="n">
         <v>1</v>
@@ -20938,7 +20938,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -21565,7 +21565,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/06/inyear.xlsx
+++ b/docs/d/06/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,11 @@
       <c r="AB75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -9602,7 +9606,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -11945,7 +11953,11 @@
       <c r="AB112" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">

--- a/docs/d/06/inyear.xlsx
+++ b/docs/d/06/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 89 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 79 clubs short</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2813,8 +2813,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4500,8 +4500,8 @@
       <c r="Y38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" s="9" t="n">
-        <v>0</v>
+      <c r="Z38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA38" s="10" t="n">
         <v>1</v>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5793,8 +5793,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -9274,7 +9274,7 @@
         <v>0</v>
       </c>
       <c r="S86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" s="10" t="n">
         <v>1</v>
@@ -10040,7 +10040,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10110,8 +10110,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10260,13 +10260,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -11773,7 +11773,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11843,8 +11843,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -12423,7 +12423,7 @@
         <v>1</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
@@ -13967,7 +13967,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14037,8 +14037,8 @@
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -14860,7 +14860,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14912,8 +14912,8 @@
       <c r="S142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T142" s="9" t="n">
-        <v>0</v>
+      <c r="T142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U142" s="9" t="n">
         <v>0</v>
@@ -16177,7 +16177,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16247,8 +16247,8 @@
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="9" t="n">
-        <v>0</v>
+      <c r="Z155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA155" s="10" t="n">
         <v>1</v>
@@ -17910,7 +17910,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -17954,7 +17954,7 @@
         <v>2</v>
       </c>
       <c r="Q172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R172" s="9" t="n">
         <v>0</v>
@@ -17980,8 +17980,8 @@
       <c r="Y172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z172" s="9" t="n">
-        <v>0</v>
+      <c r="Z172" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA172" s="10" t="n">
         <v>1</v>
@@ -18112,7 +18112,7 @@
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -18182,8 +18182,8 @@
       <c r="Y174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z174" s="9" t="n">
-        <v>0</v>
+      <c r="Z174" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA174" s="10" t="n">
         <v>1</v>
@@ -19027,7 +19027,7 @@
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>10</v>
@@ -19097,8 +19097,8 @@
       <c r="Y183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z183" s="9" t="n">
-        <v>0</v>
+      <c r="Z183" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA183" s="10" t="n">
         <v>1</v>
@@ -20620,7 +20620,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -20719,7 +20719,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -20785,7 +20785,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -21049,7 +21049,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -21148,7 +21148,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -21280,7 +21280,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -21346,7 +21346,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -21412,7 +21412,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -21511,7 +21511,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -21544,7 +21544,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -21610,7 +21610,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/06/inyear.xlsx
+++ b/docs/d/06/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 79 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 42 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>1</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>0</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1017,8 +1017,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1217,8 +1217,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1520,8 +1520,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1819,8 +1819,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2118,8 +2118,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2417,8 +2417,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2912,8 +2912,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4203,8 +4203,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4302,8 +4302,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4578,8 +4578,8 @@
       <c r="R39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="9" t="n">
-        <v>1</v>
+      <c r="S39" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T39" s="10" t="n">
         <v>1</v>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4896,8 +4896,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5595,8 +5595,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6090,8 +6090,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6393,8 +6393,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7072,8 +7072,8 @@
       <c r="S64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T64" s="9" t="n">
-        <v>0</v>
+      <c r="T64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="9" t="n">
         <v>0</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7331,13 +7331,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7387,8 +7387,8 @@
       <c r="Y67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" s="9" t="n">
-        <v>0</v>
+      <c r="Z67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA67" s="10" t="n">
         <v>1</v>
@@ -7416,7 +7416,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7486,8 +7486,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7884,8 +7884,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -8917,7 +8917,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8987,8 +8987,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -9123,7 +9123,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9193,8 +9193,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9224,7 +9224,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9294,8 +9294,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9395,8 +9395,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9496,8 +9496,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -9834,7 +9834,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9904,8 +9904,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -10448,7 +10448,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" s="9" t="n">
         <v>0</v>
@@ -10500,8 +10500,8 @@
       <c r="S98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T98" s="9" t="n">
-        <v>0</v>
+      <c r="T98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U98" s="9" t="n">
         <v>0</v>
@@ -10856,7 +10856,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10926,8 +10926,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11264,7 +11264,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11334,8 +11334,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11409,7 +11409,7 @@
         <v>2</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
@@ -11874,7 +11874,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11926,8 +11926,8 @@
       <c r="S112" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T112" s="9" t="n">
-        <v>0</v>
+      <c r="T112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
@@ -13243,8 +13243,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="9" t="n">
         <v>0</v>
@@ -13511,7 +13511,7 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q128" s="9" t="n">
         <v>0</v>
@@ -13967,7 +13967,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14019,8 +14019,8 @@
       <c r="S133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T133" s="9" t="n">
-        <v>0</v>
+      <c r="T133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U133" s="9" t="n">
         <v>0</v>
@@ -14860,7 +14860,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14930,8 +14930,8 @@
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15330,8 +15330,8 @@
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
@@ -15567,7 +15567,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15637,8 +15637,8 @@
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="9" t="n">
-        <v>0</v>
+      <c r="Z149" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA149" s="10" t="n">
         <v>1</v>
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15738,8 +15738,8 @@
       <c r="Y150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" s="9" t="n">
-        <v>0</v>
+      <c r="Z150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA150" s="10" t="n">
         <v>1</v>
@@ -15769,7 +15769,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15839,8 +15839,8 @@
       <c r="Y151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="9" t="n">
-        <v>0</v>
+      <c r="Z151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA151" s="10" t="n">
         <v>1</v>
@@ -16383,7 +16383,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16453,8 +16453,8 @@
       <c r="Y157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="9" t="n">
-        <v>0</v>
+      <c r="Z157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA157" s="10" t="n">
         <v>1</v>
@@ -16839,7 +16839,7 @@
         <v>2</v>
       </c>
       <c r="Q161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R161" s="9" t="n">
         <v>0</v>
@@ -17063,8 +17063,8 @@
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="9" t="n">
-        <v>0</v>
+      <c r="Z163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA163" s="9" t="n">
         <v>0</v>
@@ -17195,7 +17195,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17265,8 +17265,8 @@
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="9" t="n">
-        <v>0</v>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
@@ -17401,7 +17401,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17471,8 +17471,8 @@
       <c r="Y167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" s="9" t="n">
-        <v>0</v>
+      <c r="Z167" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA167" s="10" t="n">
         <v>1</v>
@@ -18318,7 +18318,7 @@
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18388,8 +18388,8 @@
       <c r="Y176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z176" s="9" t="n">
-        <v>0</v>
+      <c r="Z176" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA176" s="10" t="n">
         <v>1</v>
@@ -18662,7 +18662,7 @@
         </is>
       </c>
       <c r="P179" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q179" s="9" t="n">
         <v>1</v>
@@ -18772,7 +18772,7 @@
         <v>0</v>
       </c>
       <c r="S180" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T180" s="9" t="n">
         <v>0</v>
@@ -19233,7 +19233,7 @@
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>10</v>
@@ -19303,8 +19303,8 @@
       <c r="Y185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z185" s="9" t="n">
-        <v>0</v>
+      <c r="Z185" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA185" s="10" t="n">
         <v>1</v>
@@ -19883,7 +19883,7 @@
         <v>0</v>
       </c>
       <c r="Q191" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R191" s="9" t="n">
         <v>0</v>
@@ -19985,7 +19985,7 @@
         </is>
       </c>
       <c r="P192" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q192" s="9" t="n">
         <v>1</v>
@@ -20521,7 +20521,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -20554,7 +20554,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -20587,7 +20587,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -20620,7 +20620,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -20719,7 +20719,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -20752,7 +20752,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -20785,7 +20785,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -20818,7 +20818,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -20851,7 +20851,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -20884,7 +20884,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -20917,7 +20917,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -20983,7 +20983,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -21016,7 +21016,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -21049,7 +21049,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -21082,7 +21082,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -21115,7 +21115,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -21148,7 +21148,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -21280,7 +21280,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -21346,7 +21346,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -21379,7 +21379,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -21412,7 +21412,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -21445,7 +21445,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -21478,7 +21478,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -21544,7 +21544,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -21610,7 +21610,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/06/inyear.xlsx
+++ b/docs/d/06/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$199</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 42 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 43 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC196"/>
+  <dimension ref="A1:AC199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1464,13 +1464,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1763,13 +1763,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2161,13 +2161,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2361,13 +2361,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2757,13 +2757,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="9" t="n">
         <v>0</v>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3155,13 +3155,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3254,13 +3254,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3353,13 +3353,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3454,17 +3454,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M28" s="8" t="n">
@@ -3553,13 +3553,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3652,13 +3652,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3751,13 +3751,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3850,13 +3850,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3949,13 +3949,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4048,13 +4048,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4147,13 +4147,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4185,8 +4185,8 @@
       <c r="S35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T35" s="9" t="n">
-        <v>0</v>
+      <c r="T35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U35" s="9" t="n">
         <v>0</v>
@@ -4246,13 +4246,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4444,13 +4444,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4543,13 +4543,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4642,13 +4642,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4840,17 +4840,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -4884,11 +4884,11 @@
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" s="9" t="n">
-        <v>0</v>
+      <c r="V42" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X42" s="9" t="n">
         <v>2</v>
@@ -4941,13 +4941,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5143,13 +5143,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5280,14 +5280,14 @@
       <c r="S46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T46" s="9" t="n">
-        <v>0</v>
+      <c r="T46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5440,13 +5440,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5539,13 +5539,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5638,13 +5638,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5836,13 +5836,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6034,13 +6034,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6236,17 +6236,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6438,13 +6438,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6539,13 +6539,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6638,13 +6638,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6836,13 +6836,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6935,13 +6935,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7133,13 +7133,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7232,13 +7232,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7430,13 +7430,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7628,13 +7628,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7727,13 +7727,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7929,13 +7929,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8129,17 +8129,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8234,13 +8234,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8333,13 +8333,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8432,17 +8432,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8531,13 +8531,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8630,13 +8630,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8731,13 +8731,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -8776,7 +8776,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -8830,13 +8830,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8931,17 +8931,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -9123,7 +9123,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9175,8 +9175,8 @@
       <c r="S85" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
@@ -9238,13 +9238,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9339,17 +9339,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9440,13 +9440,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9541,17 +9541,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9646,13 +9646,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9747,13 +9747,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9773,8 +9773,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P91" s="9" t="n">
-        <v>3</v>
+      <c r="P91" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -9848,13 +9848,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10054,13 +10054,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10155,13 +10155,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10260,13 +10260,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10361,13 +10361,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10462,13 +10462,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10563,17 +10563,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10668,13 +10668,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10769,13 +10769,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10870,13 +10870,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10971,13 +10971,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11015,11 +11015,11 @@
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" s="9" t="n">
-        <v>0</v>
+      <c r="V103" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W103" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X103" s="9" t="n">
         <v>0</v>
@@ -11072,13 +11072,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11173,17 +11173,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>1</v>
@@ -11264,7 +11264,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11278,13 +11278,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11316,8 +11316,8 @@
       <c r="S106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T106" s="9" t="n">
-        <v>0</v>
+      <c r="T106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U106" s="9" t="n">
         <v>0</v>
@@ -11379,13 +11379,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11484,13 +11484,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11585,13 +11585,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -11630,7 +11630,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11664,11 +11664,11 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>82</v>
+        <v>28679927</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Russell H Conwell Club</t>
+          <t>Rise and Shine Toastmasters</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -11686,17 +11686,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L110" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -11731,26 +11731,24 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X110" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z110" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB110" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="AB110" s="4" t="n"/>
       <c r="AC110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
@@ -11765,15 +11763,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>568</v>
+        <v>82</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Stagecoach Speakers - Early Risers</t>
+          <t>Russell H Conwell Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11787,13 +11785,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11814,32 +11812,32 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q111" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S111" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T111" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="W111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X111" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
@@ -11850,7 +11848,7 @@
         <v>1</v>
       </c>
       <c r="AB111" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AC111" s="4" t="inlineStr"/>
     </row>
@@ -11866,39 +11864,39 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>6594</v>
+        <v>568</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Stagecoach Speakers Downtown East - Minneapolis</t>
+          <t>Stagecoach Speakers - Early Risers</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J112" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K112" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F112" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G112" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I112" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="J112" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="K112" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -11915,10 +11913,10 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -11932,11 +11930,11 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>1</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>6</v>
@@ -11951,13 +11949,9 @@
         <v>1</v>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC112" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="AC112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -11971,15 +11965,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>28677224</v>
+        <v>6594</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>USB Corporate Bank Toastmasters</t>
+          <t>Stagecoach Speakers Downtown East - Minneapolis</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11993,17 +11987,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -12029,36 +12023,40 @@
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X113" s="9" t="n">
-        <v>0</v>
+      <c r="X113" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC113" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -12072,15 +12070,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>6553</v>
+        <v>28677224</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Word Merchants Club</t>
+          <t>USB Corporate Bank Toastmasters</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12094,13 +12092,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12121,7 +12119,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -12144,40 +12142,40 @@
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X114" s="10" t="n">
-        <v>4</v>
+      <c r="X114" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="10" t="n">
-        <v>1</v>
+      <c r="Z114" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>1502891</v>
+        <v>6553</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Deliver Under Pressure</t>
+          <t>Word Merchants Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -12195,17 +12193,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -12222,7 +12220,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>0</v>
@@ -12246,7 +12244,7 @@
         <v>0</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -12257,7 +12255,9 @@
       <c r="AA115" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB115" s="4" t="n"/>
+      <c r="AB115" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="AC115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
@@ -12272,15 +12272,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>1311729</v>
+        <v>1502891</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Elk River Area Toastmasters</t>
+          <t>Deliver Under Pressure</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12294,17 +12294,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L116" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12338,8 +12338,8 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>1</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12371,11 +12371,11 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>28679006</v>
+        <v>1311729</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Gen AI Speakers Toastmasters</t>
+          <t>Elk River Area Toastmasters</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
@@ -12393,17 +12393,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12420,10 +12420,10 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
@@ -12444,7 +12444,7 @@
         <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12470,11 +12470,11 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>5172</v>
+        <v>28679006</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Happy Talkers Club</t>
+          <t>Gen AI Speakers Toastmasters</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
@@ -12492,13 +12492,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>3</v>
+        <v>-12</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12519,10 +12519,10 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R118" s="9" t="n">
         <v>0</v>
@@ -12537,13 +12537,13 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X118" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12569,11 +12569,11 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>3939</v>
+        <v>5172</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Power Up Toastmasters Club</t>
+          <t>Happy Talkers Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -12594,10 +12594,10 @@
         <v>10</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12618,10 +12618,10 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
@@ -12636,13 +12636,13 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X119" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -12653,9 +12653,7 @@
       <c r="AA119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB119" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB119" s="4" t="n"/>
       <c r="AC119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
@@ -12666,15 +12664,15 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>5948</v>
+        <v>3939</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>NW Metro Toastmasters</t>
+          <t>Power Up Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
@@ -12692,13 +12690,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12728,7 +12726,7 @@
         <v>0</v>
       </c>
       <c r="S120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T120" s="9" t="n">
         <v>0</v>
@@ -12737,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -12754,7 +12752,9 @@
       <c r="AA120" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB120" s="4" t="n"/>
+      <c r="AB120" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AC120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
@@ -12769,15 +12769,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>6602725</v>
+        <v>5948</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Readership Toastmasters</t>
+          <t>NW Metro Toastmasters</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12791,13 +12791,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12827,22 +12827,22 @@
         <v>0</v>
       </c>
       <c r="S121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U121" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -12868,15 +12868,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>2140</v>
+        <v>6602725</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Sunrisers Club</t>
+          <t>Readership Toastmasters</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12890,13 +12890,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -12928,20 +12928,20 @@
       <c r="S122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" s="9" t="n">
-        <v>0</v>
+      <c r="T122" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X122" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -12967,11 +12967,11 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>5342839</v>
+        <v>2140</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>The Leaders Club Toastmasters</t>
+          <t>Sunrisers Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
@@ -12989,13 +12989,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13034,13 +13034,13 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X123" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -13066,11 +13066,11 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28679026</v>
+        <v>5342839</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Watermasters</t>
+          <t>The Leaders Club Toastmasters</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
@@ -13088,17 +13088,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -13133,13 +13133,13 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="9" t="n">
-        <v>1</v>
+      <c r="X124" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -13161,19 +13161,19 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>28677684</v>
+        <v>28679026</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Building New Hope</t>
+          <t>Watermasters</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13187,13 +13187,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -13201,11 +13201,11 @@
         </is>
       </c>
       <c r="M125" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O125" s="7" t="inlineStr">
@@ -13232,13 +13232,13 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X125" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13246,8 +13246,8 @@
       <c r="Z125" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA125" s="9" t="n">
-        <v>0</v>
+      <c r="AA125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB125" s="4" t="n"/>
       <c r="AC125" s="4" t="inlineStr"/>
@@ -13264,11 +13264,11 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>1640675</v>
+        <v>28677684</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Golden Toastmasters</t>
+          <t>Building New Hope</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
@@ -13286,25 +13286,25 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L126" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N126" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O126" s="7" t="inlineStr">
@@ -13322,7 +13322,7 @@
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T126" s="9" t="n">
         <v>0</v>
@@ -13330,14 +13330,14 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>1</v>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X126" s="10" t="n">
-        <v>7</v>
+      <c r="X126" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -13345,8 +13345,8 @@
       <c r="Z126" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA126" s="10" t="n">
-        <v>1</v>
+      <c r="AA126" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB126" s="4" t="n"/>
       <c r="AC126" s="4" t="inlineStr"/>
@@ -13363,11 +13363,11 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>2312</v>
+        <v>1640675</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Mills Early Risers Club</t>
+          <t>Golden Toastmasters</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
@@ -13385,17 +13385,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13421,7 +13421,7 @@
         <v>0</v>
       </c>
       <c r="S127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127" s="9" t="n">
         <v>0</v>
@@ -13430,7 +13430,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13462,15 +13462,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>1891</v>
+        <v>2312</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Pillsbury Club</t>
+          <t>Mills Early Risers Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13484,13 +13484,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13522,11 +13522,11 @@
       <c r="S128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" s="9" t="n">
-        <v>0</v>
+      <c r="T128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V128" s="9" t="n">
         <v>0</v>
@@ -13540,8 +13540,8 @@
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -13557,19 +13557,19 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>8067</v>
+        <v>1891</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Allianz Toasters</t>
+          <t>Pillsbury Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13583,17 +13583,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q129" s="9" t="n">
         <v>0</v>
@@ -13628,19 +13628,19 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X129" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="10" t="n">
-        <v>1</v>
+      <c r="Z129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13660,15 +13660,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>6595587</v>
+        <v>8067</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Sogeti Storytellers</t>
+          <t>Allianz Toasters</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13682,17 +13682,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L130" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -13727,26 +13727,24 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X130" s="9" t="n">
-        <v>0</v>
+      <c r="X130" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB130" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB130" s="4" t="n"/>
       <c r="AC130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
@@ -13761,11 +13759,11 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>1789</v>
+        <v>6595587</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Speakeasy Club</t>
+          <t>Sogeti Storytellers</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -13783,13 +13781,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -13810,10 +13808,10 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>0</v>
@@ -13828,13 +13826,13 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X131" s="10" t="n">
-        <v>4</v>
+      <c r="X131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -13845,7 +13843,9 @@
       <c r="AA131" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB131" s="4" t="n"/>
+      <c r="AB131" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AC131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
@@ -13860,11 +13860,11 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>4375</v>
+        <v>1789</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>SRF Toastmaster Club</t>
+          <t>Speakeasy Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
@@ -13882,13 +13882,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13896,11 +13896,11 @@
         </is>
       </c>
       <c r="M132" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O132" s="7" t="inlineStr">
@@ -13909,10 +13909,10 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R132" s="9" t="n">
         <v>0</v>
@@ -13932,8 +13932,8 @@
       <c r="W132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X132" s="9" t="n">
-        <v>0</v>
+      <c r="X132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
@@ -13941,8 +13941,8 @@
       <c r="Z132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA132" s="9" t="n">
-        <v>0</v>
+      <c r="AA132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB132" s="4" t="n"/>
       <c r="AC132" s="4" t="inlineStr"/>
@@ -13959,15 +13959,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>1286458</v>
+        <v>4375</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Tech Masters-Twin Cities</t>
+          <t>SRF Toastmaster Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13981,10 +13981,10 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K133" s="4" t="n">
         <v>0</v>
@@ -13995,11 +13995,11 @@
         </is>
       </c>
       <c r="M133" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O133" s="7" t="inlineStr">
@@ -14011,7 +14011,7 @@
         <v>0</v>
       </c>
       <c r="Q133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -14019,8 +14019,8 @@
       <c r="S133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T133" s="10" t="n">
-        <v>1</v>
+      <c r="T133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U133" s="9" t="n">
         <v>0</v>
@@ -14031,21 +14031,19 @@
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X133" s="10" t="n">
-        <v>4</v>
+      <c r="X133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA133" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB133" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="Z133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" s="4" t="n"/>
       <c r="AC133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
@@ -14060,11 +14058,11 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>6144</v>
+        <v>1286458</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Whole Wheat Toastmasters Club</t>
+          <t>Tech Masters-Twin Cities</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
@@ -14082,17 +14080,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -14109,10 +14107,10 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
@@ -14127,13 +14125,13 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X134" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -14144,7 +14142,9 @@
       <c r="AA134" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB134" s="4" t="n"/>
+      <c r="AB134" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AC134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
@@ -14155,19 +14155,19 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>5913</v>
+        <v>6144</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Cargill Trademasters Club</t>
+          <t>Whole Wheat Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14181,13 +14181,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14208,10 +14208,10 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q135" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R135" s="9" t="n">
         <v>0</v>
@@ -14219,8 +14219,8 @@
       <c r="S135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T135" s="9" t="n">
-        <v>0</v>
+      <c r="T135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U135" s="9" t="n">
         <v>0</v>
@@ -14232,7 +14232,7 @@
         <v>0</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -14258,11 +14258,11 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>1746748</v>
+        <v>5913</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>PowerTalk Toastmasters</t>
+          <t>Cargill Trademasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
@@ -14280,13 +14280,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>0</v>
       </c>
       <c r="Q136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
@@ -14325,13 +14325,13 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X136" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
@@ -14357,11 +14357,11 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>1055613</v>
+        <v>1746748</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Spirit of Leadership</t>
+          <t>PowerTalk Toastmasters</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
@@ -14382,10 +14382,10 @@
         <v>14</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>0</v>
       </c>
       <c r="X137" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
@@ -14456,11 +14456,11 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>6348</v>
+        <v>1055613</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>TicTalkers Toastmasters Club</t>
+          <t>Spirit of Leadership</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
@@ -14478,13 +14478,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14555,15 +14555,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>2119</v>
+        <v>6348</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Tonka Talkers</t>
+          <t>TicTalkers Toastmasters Club</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14577,13 +14577,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -14633,8 +14633,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -14654,15 +14654,15 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>7541</v>
+        <v>2119</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Words-Of-Mouth Club</t>
+          <t>Tonka Talkers</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14676,13 +14676,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14706,22 +14706,22 @@
         <v>0</v>
       </c>
       <c r="Q140" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S140" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T140" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U140" s="10" t="n">
-        <v>1</v>
+      <c r="S140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -14732,8 +14732,8 @@
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="10" t="n">
-        <v>1</v>
+      <c r="Z140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -14744,24 +14744,24 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>1982188</v>
+        <v>7541</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Data Park Toasters</t>
+          <t>Words-Of-Mouth Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14775,13 +14775,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14805,19 +14805,19 @@
         <v>0</v>
       </c>
       <c r="Q141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U141" s="9" t="n">
-        <v>0</v>
+      <c r="S141" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T141" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V141" s="9" t="n">
         <v>0</v>
@@ -14826,13 +14826,13 @@
         <v>0</v>
       </c>
       <c r="X141" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -14852,15 +14852,15 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>388</v>
+        <v>1982188</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Lakers Toastmasters Club #388</t>
+          <t>Data Park Toasters</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14874,13 +14874,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -14912,33 +14912,31 @@
       <c r="S142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T142" s="10" t="n">
-        <v>1</v>
+      <c r="T142" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X142" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="10" t="n">
-        <v>1</v>
+      <c r="Z142" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB142" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="AB142" s="4" t="n"/>
       <c r="AC142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
@@ -14953,11 +14951,11 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>691684</v>
+        <v>388</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Leadership Summit</t>
+          <t>Lakers Toastmasters Club #388</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
@@ -14975,13 +14973,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15037,7 +15035,9 @@
       <c r="AA143" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB143" s="4" t="n"/>
+      <c r="AB143" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AC143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
@@ -15052,15 +15052,15 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>4953</v>
+        <v>691684</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Noontime Talkers Club</t>
+          <t>Leadership Summit</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15074,13 +15074,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15112,26 +15112,26 @@
       <c r="S144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T144" s="9" t="n">
-        <v>0</v>
+      <c r="T144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X144" s="9" t="n">
-        <v>2</v>
+      <c r="X144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA144" s="10" t="n">
         <v>1</v>
@@ -15151,15 +15151,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>1459079</v>
+        <v>4953</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Up and Optum Toastmasters</t>
+          <t>Noontime Talkers Club</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15173,13 +15173,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>0</v>
       </c>
       <c r="S145" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T145" s="9" t="n">
         <v>0</v>
@@ -15218,26 +15218,24 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X145" s="10" t="n">
-        <v>5</v>
+      <c r="X145" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="10" t="n">
-        <v>1</v>
+      <c r="Z145" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB145" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="AB145" s="4" t="n"/>
       <c r="AC145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
@@ -15248,19 +15246,19 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>6446</v>
+        <v>1459079</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>MY-T Speakers Toastmasters Club</t>
+          <t>Up and Optum Toastmasters</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15274,13 +15272,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15310,16 +15308,16 @@
         <v>0</v>
       </c>
       <c r="S146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U146" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -15353,11 +15351,11 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>2342360</v>
+        <v>6446</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>OPTUMists</t>
+          <t>MY-T Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
@@ -15375,13 +15373,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15402,7 +15400,7 @@
         </is>
       </c>
       <c r="P147" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q147" s="9" t="n">
         <v>0</v>
@@ -15420,7 +15418,7 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15438,7 +15436,7 @@
         <v>1</v>
       </c>
       <c r="AB147" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC147" s="4" t="inlineStr"/>
     </row>
@@ -15454,15 +15452,15 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>9218</v>
+        <v>2342360</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Speakers After Hours Toastmasters Club</t>
+          <t>OPTUMists</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15476,13 +15474,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15506,13 +15504,13 @@
         <v>1</v>
       </c>
       <c r="Q148" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S148" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T148" s="9" t="n">
         <v>0</v>
@@ -15521,31 +15519,27 @@
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X148" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="9" t="n">
-        <v>0</v>
+      <c r="Z148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA148" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB148" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC148" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -15559,15 +15553,15 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>1098516</v>
+        <v>9218</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Super Communicators</t>
+          <t>Speakers After Hours Toastmasters Club</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15581,13 +15575,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15608,16 +15602,16 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R149" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T149" s="9" t="n">
         <v>0</v>
@@ -15626,27 +15620,31 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X149" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="10" t="n">
-        <v>1</v>
+      <c r="Z149" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA149" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB149" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC149" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC149" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -15660,15 +15658,15 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>4701</v>
+        <v>1098516</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Super Speakers Club</t>
+          <t>Super Communicators</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15682,13 +15680,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -15720,8 +15718,8 @@
       <c r="S150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T150" s="10" t="n">
-        <v>1</v>
+      <c r="T150" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U150" s="9" t="n">
         <v>0</v>
@@ -15733,7 +15731,7 @@
         <v>0</v>
       </c>
       <c r="X150" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y150" s="9" t="n">
         <v>0</v>
@@ -15745,7 +15743,7 @@
         <v>1</v>
       </c>
       <c r="AB150" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC150" s="4" t="inlineStr"/>
     </row>
@@ -15757,19 +15755,19 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>2512</v>
+        <v>4701</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Confident Communicators Toastmasters 2512</t>
+          <t>Super Speakers Club</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15783,13 +15781,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -15821,11 +15819,11 @@
       <c r="S151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U151" s="9" t="n">
-        <v>0</v>
+      <c r="T151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V151" s="9" t="n">
         <v>0</v>
@@ -15833,8 +15831,8 @@
       <c r="W151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X151" s="9" t="n">
-        <v>0</v>
+      <c r="X151" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
@@ -15846,7 +15844,7 @@
         <v>1</v>
       </c>
       <c r="AB151" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC151" s="4" t="inlineStr"/>
     </row>
@@ -15862,15 +15860,15 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>1280</v>
+        <v>2512</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Dan Patch Toastmasters Club</t>
+          <t>Confident Communicators Toastmasters 2512</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -15884,17 +15882,17 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L152" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M152" s="8" t="n">
@@ -15911,7 +15909,7 @@
         </is>
       </c>
       <c r="P152" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q152" s="9" t="n">
         <v>0</v>
@@ -15922,20 +15920,20 @@
       <c r="S152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T152" s="10" t="n">
-        <v>1</v>
+      <c r="T152" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X152" s="10" t="n">
-        <v>7</v>
+      <c r="X152" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
@@ -15947,13 +15945,9 @@
         <v>1</v>
       </c>
       <c r="AB152" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC152" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -15967,15 +15961,15 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>28676290</v>
+        <v>1280</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>H2Orators</t>
+          <t>Dan Patch Toastmasters Club</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -15989,25 +15983,25 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M153" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N153" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O153" s="7" t="inlineStr">
@@ -16016,7 +16010,7 @@
         </is>
       </c>
       <c r="P153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q153" s="9" t="n">
         <v>0</v>
@@ -16027,34 +16021,38 @@
       <c r="S153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T153" s="9" t="n">
-        <v>0</v>
+      <c r="T153" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U153" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X153" s="9" t="n">
-        <v>0</v>
+      <c r="X153" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA153" s="9" t="n">
-        <v>0</v>
+      <c r="Z153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA153" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB153" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC153" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC153" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -16068,15 +16066,15 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>28678694</v>
+        <v>28676290</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>MarketPointe Drive Club</t>
+          <t>H2Orators</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16090,25 +16088,25 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N154" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O154" s="7" t="inlineStr">
@@ -16117,7 +16115,7 @@
         </is>
       </c>
       <c r="P154" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q154" s="9" t="n">
         <v>0</v>
@@ -16140,20 +16138,20 @@
       <c r="W154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X154" s="10" t="n">
-        <v>4</v>
+      <c r="X154" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA154" s="10" t="n">
-        <v>1</v>
+      <c r="Z154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA154" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB154" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC154" s="4" t="inlineStr"/>
     </row>
@@ -16169,15 +16167,15 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>1000</v>
+        <v>28678694</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Midday Mumblers Club</t>
+          <t>MarketPointe Drive Club</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16191,17 +16189,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L155" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M155" s="8" t="n">
@@ -16218,31 +16216,31 @@
         </is>
       </c>
       <c r="P155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q155" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S155" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T155" s="10" t="n">
-        <v>1</v>
+      <c r="S155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U155" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V155" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X155" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y155" s="9" t="n">
         <v>0</v>
@@ -16254,13 +16252,9 @@
         <v>1</v>
       </c>
       <c r="AB155" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC155" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -16274,15 +16268,15 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>2376</v>
+        <v>1000</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Spartan Speakers Club</t>
+          <t>Midday Mumblers Club</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16299,10 +16293,10 @@
         <v>10</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16326,28 +16320,28 @@
         <v>0</v>
       </c>
       <c r="Q156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T156" s="9" t="n">
-        <v>0</v>
+      <c r="S156" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U156" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X156" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y156" s="9" t="n">
         <v>0</v>
@@ -16359,9 +16353,13 @@
         <v>1</v>
       </c>
       <c r="AB156" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC156" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC156" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -16371,19 +16369,19 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>3406456</v>
+        <v>2376</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>3M Hutchinson Toastmasters Club</t>
+          <t>Spartan Speakers Club</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16400,10 +16398,10 @@
         <v>10</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16432,23 +16430,23 @@
       <c r="R157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S157" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T157" s="10" t="n">
-        <v>1</v>
+      <c r="S157" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U157" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X157" s="9" t="n">
-        <v>2</v>
+      <c r="X157" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y157" s="9" t="n">
         <v>0</v>
@@ -16476,15 +16474,15 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>4324</v>
+        <v>3406456</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Hutchinson Toastmasters II</t>
+          <t>3M Hutchinson Toastmasters Club</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -16498,17 +16496,17 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L158" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M158" s="8" t="n">
@@ -16525,7 +16523,7 @@
         </is>
       </c>
       <c r="P158" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q158" s="9" t="n">
         <v>0</v>
@@ -16533,23 +16531,23 @@
       <c r="R158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T158" s="9" t="n">
-        <v>0</v>
+      <c r="S158" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T158" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U158" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V158" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X158" s="10" t="n">
-        <v>7</v>
+      <c r="X158" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y158" s="9" t="n">
         <v>0</v>
@@ -16561,13 +16559,9 @@
         <v>1</v>
       </c>
       <c r="AB158" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC158" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -16581,15 +16575,15 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>28679049</v>
+        <v>4324</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Life Time Minnesota</t>
+          <t>Hutchinson Toastmasters II</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16603,13 +16597,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -16617,11 +16611,11 @@
         </is>
       </c>
       <c r="M159" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N159" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O159" s="7" t="inlineStr">
@@ -16630,7 +16624,7 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q159" s="9" t="n">
         <v>0</v>
@@ -16648,27 +16642,31 @@
         <v>0</v>
       </c>
       <c r="V159" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X159" s="9" t="n">
-        <v>0</v>
+      <c r="X159" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z159" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA159" s="9" t="n">
-        <v>0</v>
+      <c r="Z159" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB159" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC159" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC159" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -16682,15 +16680,15 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>5053</v>
+        <v>28679049</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Tri-County Toastmasters</t>
+          <t>Life Time Minnesota</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16704,13 +16702,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
@@ -16718,11 +16716,11 @@
         </is>
       </c>
       <c r="M160" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N160" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O160" s="7" t="inlineStr">
@@ -16731,7 +16729,7 @@
         </is>
       </c>
       <c r="P160" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q160" s="9" t="n">
         <v>0</v>
@@ -16754,26 +16752,22 @@
       <c r="W160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X160" s="10" t="n">
-        <v>6</v>
+      <c r="X160" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA160" s="10" t="n">
-        <v>1</v>
+      <c r="Z160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA160" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB160" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC160" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -16787,15 +16781,15 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>841690</v>
+        <v>5053</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Tri-Dynamics</t>
+          <t>Tri-County Toastmasters</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -16809,13 +16803,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -16836,10 +16830,10 @@
         </is>
       </c>
       <c r="P161" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q161" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R161" s="9" t="n">
         <v>0</v>
@@ -16853,14 +16847,14 @@
       <c r="U161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V161" s="10" t="n">
-        <v>4</v>
+      <c r="V161" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X161" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y161" s="9" t="n">
         <v>0</v>
@@ -16871,8 +16865,14 @@
       <c r="AA161" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB161" s="4" t="n"/>
-      <c r="AC161" s="4" t="inlineStr"/>
+      <c r="AB161" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC161" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -16886,15 +16886,15 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>4340844</v>
+        <v>841690</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Uncommon Speakers</t>
+          <t>Tri-Dynamics</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -16908,13 +16908,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -16935,10 +16935,10 @@
         </is>
       </c>
       <c r="P162" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R162" s="9" t="n">
         <v>0</v>
@@ -16952,20 +16952,20 @@
       <c r="U162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V162" s="9" t="n">
-        <v>1</v>
+      <c r="V162" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X162" s="9" t="n">
-        <v>0</v>
+      <c r="X162" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z162" s="9" t="n">
-        <v>0</v>
+      <c r="Z162" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA162" s="10" t="n">
         <v>1</v>
@@ -16981,15 +16981,15 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>515</v>
+        <v>4340844</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Cosmopolitan Toastmasters Club</t>
+          <t>Uncommon Speakers</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
@@ -17007,13 +17007,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -17021,11 +17021,11 @@
         </is>
       </c>
       <c r="M163" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N163" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O163" s="7" t="inlineStr">
@@ -17052,7 +17052,7 @@
         <v>0</v>
       </c>
       <c r="V163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
@@ -17063,15 +17063,13 @@
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA163" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB163" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z163" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA163" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB163" s="4" t="n"/>
       <c r="AC163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
@@ -17086,15 +17084,15 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>1083844</v>
+        <v>515</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>On The Road Again</t>
+          <t>Cosmopolitan Toastmasters Club</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -17108,25 +17106,25 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L164" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M164" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N164" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O164" s="7" t="inlineStr">
@@ -17158,8 +17156,8 @@
       <c r="W164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X164" s="10" t="n">
-        <v>5</v>
+      <c r="X164" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y164" s="9" t="n">
         <v>0</v>
@@ -17167,11 +17165,11 @@
       <c r="Z164" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA164" s="10" t="n">
-        <v>1</v>
+      <c r="AA164" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB164" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC164" s="4" t="inlineStr"/>
     </row>
@@ -17187,11 +17185,11 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>8194</v>
+        <v>1083844</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Sea Speakers Club</t>
+          <t>On The Road Again</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
@@ -17209,13 +17207,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
@@ -17254,13 +17252,13 @@
         <v>0</v>
       </c>
       <c r="V165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X165" s="9" t="n">
-        <v>0</v>
+      <c r="X165" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y165" s="9" t="n">
         <v>0</v>
@@ -17272,7 +17270,7 @@
         <v>1</v>
       </c>
       <c r="AB165" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC165" s="4" t="inlineStr"/>
     </row>
@@ -17288,11 +17286,11 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>7215</v>
+        <v>8194</v>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Shakopee Toastmasters</t>
+          <t>Sea Speakers Club</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
@@ -17310,10 +17308,10 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K166" s="4" t="n">
         <v>0</v>
@@ -17337,7 +17335,7 @@
         </is>
       </c>
       <c r="P166" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q166" s="9" t="n">
         <v>0</v>
@@ -17355,13 +17353,13 @@
         <v>0</v>
       </c>
       <c r="V166" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X166" s="10" t="n">
-        <v>7</v>
+      <c r="X166" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y166" s="9" t="n">
         <v>0</v>
@@ -17373,13 +17371,9 @@
         <v>1</v>
       </c>
       <c r="AB166" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC166" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -17393,11 +17387,11 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>3096</v>
+        <v>7215</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Speakers Under Pressure</t>
+          <t>Shakopee Toastmasters</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
@@ -17418,10 +17412,10 @@
         <v>11</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
@@ -17442,7 +17436,7 @@
         </is>
       </c>
       <c r="P167" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q167" s="9" t="n">
         <v>0</v>
@@ -17466,7 +17460,7 @@
         <v>0</v>
       </c>
       <c r="X167" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y167" s="9" t="n">
         <v>0</v>
@@ -17478,9 +17472,13 @@
         <v>1</v>
       </c>
       <c r="AB167" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC167" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC167" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -17494,15 +17492,15 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>4316</v>
+        <v>3096</v>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Talking Heads Club</t>
+          <t>Speakers Under Pressure</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -17516,17 +17514,17 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L168" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M168" s="8" t="n">
@@ -17552,16 +17550,16 @@
         <v>0</v>
       </c>
       <c r="S168" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T168" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T168" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U168" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W168" s="9" t="n">
         <v>0</v>
@@ -17579,13 +17577,9 @@
         <v>1</v>
       </c>
       <c r="AB168" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC168" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -17595,19 +17589,19 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>28676831</v>
+        <v>4316</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Delta Propellers</t>
+          <t>Talking Heads Club</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>10</v>
@@ -17621,17 +17615,17 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L169" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L169" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M169" s="8" t="n">
@@ -17657,36 +17651,40 @@
         <v>0</v>
       </c>
       <c r="S169" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T169" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U169" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V169" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X169" s="9" t="n">
-        <v>1</v>
+      <c r="X169" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z169" s="9" t="n">
-        <v>0</v>
+      <c r="Z169" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA169" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB169" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC169" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC169" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -17700,11 +17698,11 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>780801</v>
+        <v>28676831</v>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Generally Speaking Toastmasters</t>
+          <t>Delta Propellers</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
@@ -17722,13 +17720,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -17773,7 +17771,7 @@
         <v>0</v>
       </c>
       <c r="X170" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y170" s="9" t="n">
         <v>0</v>
@@ -17801,15 +17799,15 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>4611</v>
+        <v>780801</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Luncheon Linguists Club</t>
+          <t>Generally Speaking Toastmasters</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -17823,17 +17821,17 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L171" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M171" s="8" t="n">
@@ -17850,16 +17848,16 @@
         </is>
       </c>
       <c r="P171" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q171" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R171" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S171" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T171" s="9" t="n">
         <v>0</v>
@@ -17868,19 +17866,19 @@
         <v>0</v>
       </c>
       <c r="V171" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W171" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X171" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W171" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X171" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z171" s="10" t="n">
-        <v>1</v>
+      <c r="Z171" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA171" s="10" t="n">
         <v>1</v>
@@ -17902,15 +17900,15 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>28676184</v>
+        <v>4611</v>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Toltzmasters</t>
+          <t>Luncheon Linguists Club</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -17924,17 +17922,17 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L172" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M172" s="8" t="n">
@@ -17951,7 +17949,7 @@
         </is>
       </c>
       <c r="P172" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q172" s="9" t="n">
         <v>1</v>
@@ -17960,7 +17958,7 @@
         <v>0</v>
       </c>
       <c r="S172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T172" s="9" t="n">
         <v>0</v>
@@ -17968,50 +17966,50 @@
       <c r="U172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V172" s="9" t="n">
-        <v>0</v>
+      <c r="V172" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X172" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z172" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA172" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB172" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="Y172" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z172" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA172" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB172" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="AC172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>6227</v>
+        <v>28676184</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Apple Valley Toastmasters</t>
+          <t>Toltzmasters</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -18025,13 +18023,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J173" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
@@ -18052,10 +18050,10 @@
         </is>
       </c>
       <c r="P173" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q173" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R173" s="9" t="n">
         <v>0</v>
@@ -18076,13 +18074,13 @@
         <v>0</v>
       </c>
       <c r="X173" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z173" s="9" t="n">
-        <v>0</v>
+      <c r="Z173" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA173" s="10" t="n">
         <v>1</v>
@@ -18095,24 +18093,24 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>981</v>
+        <v>28680751</v>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Crest Toastmasters Club</t>
+          <t>UMW ToastMacsters</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -18126,17 +18124,17 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K174" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L174" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L174" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M174" s="8" t="n">
@@ -18153,7 +18151,7 @@
         </is>
       </c>
       <c r="P174" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q174" s="9" t="n">
         <v>0</v>
@@ -18164,8 +18162,8 @@
       <c r="S174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T174" s="10" t="n">
-        <v>1</v>
+      <c r="T174" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U174" s="9" t="n">
         <v>0</v>
@@ -18176,21 +18174,19 @@
       <c r="W174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X174" s="10" t="n">
-        <v>7</v>
+      <c r="X174" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y174" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z174" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA174" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB174" s="4" t="n">
-        <v>7</v>
-      </c>
+      <c r="AB174" s="4" t="n"/>
       <c r="AC174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
@@ -18205,15 +18201,15 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>3338102</v>
+        <v>6227</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Lakeville Toastmasters</t>
+          <t>Apple Valley Toastmasters</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18227,17 +18223,17 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J175" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L175" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M175" s="8" t="n">
@@ -18254,7 +18250,7 @@
         </is>
       </c>
       <c r="P175" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q175" s="9" t="n">
         <v>0</v>
@@ -18263,40 +18259,36 @@
         <v>0</v>
       </c>
       <c r="S175" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T175" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T175" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U175" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V175" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W175" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X175" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z175" s="10" t="n">
-        <v>1</v>
+      <c r="Z175" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA175" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB175" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC175" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -18310,15 +18302,15 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>9893</v>
+        <v>981</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Speak N' Eagan Club</t>
+          <t>Crest Toastmasters Club</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18332,13 +18324,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J176" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -18359,7 +18351,7 @@
         </is>
       </c>
       <c r="P176" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q176" s="9" t="n">
         <v>0</v>
@@ -18370,20 +18362,20 @@
       <c r="S176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T176" s="9" t="n">
-        <v>0</v>
+      <c r="T176" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U176" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V176" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X176" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y176" s="9" t="n">
         <v>0</v>
@@ -18395,7 +18387,7 @@
         <v>1</v>
       </c>
       <c r="AB176" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC176" s="4" t="inlineStr"/>
     </row>
@@ -18407,19 +18399,19 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>28675820</v>
+        <v>3338102</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Deltasigs Toastmasters</t>
+          <t>Lakeville Toastmasters</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -18433,13 +18425,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J177" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -18460,7 +18452,7 @@
         </is>
       </c>
       <c r="P177" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q177" s="9" t="n">
         <v>0</v>
@@ -18469,22 +18461,22 @@
         <v>0</v>
       </c>
       <c r="S177" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T177" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T177" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U177" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V177" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X177" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y177" s="9" t="n">
         <v>0</v>
@@ -18496,9 +18488,13 @@
         <v>1</v>
       </c>
       <c r="AB177" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC177" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC177" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -18508,19 +18504,19 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>5607421</v>
+        <v>28680211</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Northfield Community Toastmasters</t>
+          <t>Plant &amp; Garden Toastmasters Club</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -18534,17 +18530,17 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K178" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L178" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L178" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M178" s="8" t="n">
@@ -18561,7 +18557,7 @@
         </is>
       </c>
       <c r="P178" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q178" s="9" t="n">
         <v>0</v>
@@ -18569,11 +18565,11 @@
       <c r="R178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S178" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T178" s="9" t="n">
-        <v>0</v>
+      <c r="S178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U178" s="9" t="n">
         <v>0</v>
@@ -18584,21 +18580,19 @@
       <c r="W178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X178" s="10" t="n">
-        <v>4</v>
+      <c r="X178" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z178" s="10" t="n">
-        <v>1</v>
+      <c r="Z178" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA178" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB178" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="AB178" s="4" t="n"/>
       <c r="AC178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
@@ -18609,15 +18603,15 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>7050312</v>
+        <v>9893</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Pathways to Success Toastmasters</t>
+          <t>Speak N' Eagan Club</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
@@ -18635,13 +18629,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
@@ -18662,10 +18656,10 @@
         </is>
       </c>
       <c r="P179" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q179" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R179" s="9" t="n">
         <v>0</v>
@@ -18680,13 +18674,13 @@
         <v>0</v>
       </c>
       <c r="V179" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W179" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X179" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y179" s="9" t="n">
         <v>0</v>
@@ -18698,7 +18692,7 @@
         <v>1</v>
       </c>
       <c r="AB179" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC179" s="4" t="inlineStr"/>
     </row>
@@ -18714,11 +18708,11 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>28676958</v>
+        <v>28675820</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Poetry Masters Toastmasters</t>
+          <t>Deltasigs Toastmasters</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
@@ -18736,13 +18730,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L180" s="7" t="inlineStr">
         <is>
@@ -18772,7 +18766,7 @@
         <v>0</v>
       </c>
       <c r="S180" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T180" s="9" t="n">
         <v>0</v>
@@ -18787,7 +18781,7 @@
         <v>0</v>
       </c>
       <c r="X180" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y180" s="9" t="n">
         <v>0</v>
@@ -18799,7 +18793,7 @@
         <v>1</v>
       </c>
       <c r="AB180" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC180" s="4" t="inlineStr"/>
     </row>
@@ -18815,15 +18809,15 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>7903656</v>
+        <v>5607421</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>PR Pros</t>
+          <t>Northfield Community Toastmasters</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -18840,10 +18834,10 @@
         <v>13</v>
       </c>
       <c r="J181" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
@@ -18864,7 +18858,7 @@
         </is>
       </c>
       <c r="P181" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q181" s="9" t="n">
         <v>0</v>
@@ -18872,8 +18866,8 @@
       <c r="R181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S181" s="9" t="n">
-        <v>1</v>
+      <c r="S181" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T181" s="9" t="n">
         <v>0</v>
@@ -18882,13 +18876,13 @@
         <v>0</v>
       </c>
       <c r="V181" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W181" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X181" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y181" s="9" t="n">
         <v>0</v>
@@ -18899,7 +18893,9 @@
       <c r="AA181" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB181" s="4" t="n"/>
+      <c r="AB181" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AC181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
@@ -18914,15 +18910,15 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>6655858</v>
+        <v>7050312</v>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Valley Voices</t>
+          <t>Pathways to Success Toastmasters</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>10</v>
@@ -18936,13 +18932,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -18963,10 +18959,10 @@
         </is>
       </c>
       <c r="P182" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q182" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R182" s="9" t="n">
         <v>0</v>
@@ -18974,20 +18970,20 @@
       <c r="S182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T182" s="10" t="n">
-        <v>1</v>
+      <c r="T182" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U182" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V182" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W182" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X182" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y182" s="9" t="n">
         <v>0</v>
@@ -18999,13 +18995,9 @@
         <v>1</v>
       </c>
       <c r="AB182" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC182" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="AC182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -19015,15 +19007,15 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>175</v>
+        <v>28676958</v>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Mankato Toastmasters Club</t>
+          <t>Poetry Masters Toastmasters</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
@@ -19041,17 +19033,17 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J183" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L183" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L183" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M183" s="8" t="n">
@@ -19068,16 +19060,16 @@
         </is>
       </c>
       <c r="P183" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q183" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R183" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S183" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T183" s="9" t="n">
         <v>0</v>
@@ -19086,13 +19078,13 @@
         <v>0</v>
       </c>
       <c r="V183" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W183" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X183" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y183" s="9" t="n">
         <v>0</v>
@@ -19104,13 +19096,9 @@
         <v>1</v>
       </c>
       <c r="AB183" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC183" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -19120,19 +19108,19 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>134</v>
+        <v>7903656</v>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Owatonna Club</t>
+          <t>PR Pros</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19146,13 +19134,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -19160,11 +19148,11 @@
         </is>
       </c>
       <c r="M184" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N184" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O184" s="7" t="inlineStr">
@@ -19182,7 +19170,7 @@
         <v>0</v>
       </c>
       <c r="S184" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T184" s="9" t="n">
         <v>0</v>
@@ -19191,26 +19179,24 @@
         <v>0</v>
       </c>
       <c r="V184" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X184" s="9" t="n">
-        <v>0</v>
+      <c r="X184" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z184" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA184" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB184" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z184" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA184" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB184" s="4" t="n"/>
       <c r="AC184" s="4" t="inlineStr"/>
     </row>
     <row r="185">
@@ -19221,19 +19207,19 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>2248</v>
+        <v>6655858</v>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Speakers Of The House Club</t>
+          <t>Valley Voices</t>
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>10</v>
@@ -19250,10 +19236,10 @@
         <v>9</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
@@ -19285,8 +19271,8 @@
       <c r="S185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T185" s="9" t="n">
-        <v>0</v>
+      <c r="T185" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U185" s="9" t="n">
         <v>0</v>
@@ -19298,21 +19284,25 @@
         <v>0</v>
       </c>
       <c r="X185" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z185" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA185" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB185" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Y185" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z185" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA185" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB185" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC185" s="4" t="inlineStr"/>
+      <c r="AC185" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -19326,15 +19316,15 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>8204</v>
+        <v>175</v>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Tuesday With Toastmasters Club</t>
+          <t>Mankato Toastmasters Club</t>
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -19348,13 +19338,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J186" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
@@ -19362,11 +19352,11 @@
         </is>
       </c>
       <c r="M186" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N186" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O186" s="7" t="inlineStr">
@@ -19375,10 +19365,10 @@
         </is>
       </c>
       <c r="P186" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q186" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R186" s="9" t="n">
         <v>0</v>
@@ -19398,22 +19388,26 @@
       <c r="W186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X186" s="9" t="n">
-        <v>0</v>
+      <c r="X186" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z186" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA186" s="9" t="n">
-        <v>0</v>
+      <c r="Z186" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA186" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB186" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC186" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC186" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -19423,19 +19417,19 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>1505727</v>
+        <v>134</v>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Bright Monday</t>
+          <t>Owatonna Club</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -19449,13 +19443,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J187" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="J187" s="4" t="n">
-        <v>7</v>
-      </c>
       <c r="K187" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
@@ -19463,11 +19457,11 @@
         </is>
       </c>
       <c r="M187" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N187" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O187" s="7" t="inlineStr">
@@ -19487,20 +19481,20 @@
       <c r="S187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T187" s="10" t="n">
-        <v>1</v>
+      <c r="T187" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U187" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V187" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X187" s="10" t="n">
-        <v>5</v>
+      <c r="X187" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y187" s="9" t="n">
         <v>0</v>
@@ -19508,11 +19502,11 @@
       <c r="Z187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA187" s="10" t="n">
-        <v>1</v>
+      <c r="AA187" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB187" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC187" s="4" t="inlineStr"/>
     </row>
@@ -19524,19 +19518,19 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>4677</v>
+        <v>2248</v>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Mayo Hi-Nooners Club</t>
+          <t>Speakers Of The House Club</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>10</v>
@@ -19550,13 +19544,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J188" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L188" s="7" t="inlineStr">
         <is>
@@ -19577,7 +19571,7 @@
         </is>
       </c>
       <c r="P188" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q188" s="9" t="n">
         <v>0</v>
@@ -19594,14 +19588,14 @@
       <c r="U188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V188" s="9" t="n">
-        <v>3</v>
+      <c r="V188" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W188" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X188" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y188" s="9" t="n">
         <v>0</v>
@@ -19613,7 +19607,7 @@
         <v>1</v>
       </c>
       <c r="AB188" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC188" s="4" t="inlineStr"/>
     </row>
@@ -19625,19 +19619,19 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>8693</v>
+        <v>8204</v>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Rochester Break Of Day Toastmasters Club</t>
+          <t>Tuesday With Toastmasters Club</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -19651,13 +19645,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J189" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
@@ -19665,11 +19659,11 @@
         </is>
       </c>
       <c r="M189" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N189" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O189" s="7" t="inlineStr">
@@ -19687,10 +19681,10 @@
         <v>0</v>
       </c>
       <c r="S189" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T189" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T189" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U189" s="9" t="n">
         <v>0</v>
@@ -19701,20 +19695,20 @@
       <c r="W189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X189" s="10" t="n">
-        <v>6</v>
+      <c r="X189" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z189" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA189" s="10" t="n">
-        <v>1</v>
+      <c r="Z189" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB189" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC189" s="4" t="inlineStr"/>
     </row>
@@ -19730,15 +19724,15 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>7470</v>
+        <v>1505727</v>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Southern Minnesota Mentors Club</t>
+          <t>Bright Monday</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" s="6" t="n">
         <v>10</v>
@@ -19752,13 +19746,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J190" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -19779,31 +19773,31 @@
         </is>
       </c>
       <c r="P190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V190" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q190" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R190" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S190" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T190" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U190" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V190" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="W190" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X190" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y190" s="9" t="n">
         <v>0</v>
@@ -19815,7 +19809,7 @@
         <v>1</v>
       </c>
       <c r="AB190" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC190" s="4" t="inlineStr"/>
     </row>
@@ -19831,11 +19825,11 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>2440926</v>
+        <v>4677</v>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>TNT- Toastmasters - N - Technology</t>
+          <t>Mayo Hi-Nooners Club</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
@@ -19853,17 +19847,17 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J191" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L191" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L191" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M191" s="8" t="n">
@@ -19880,16 +19874,16 @@
         </is>
       </c>
       <c r="P191" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q191" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R191" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S191" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T191" s="9" t="n">
         <v>0</v>
@@ -19898,13 +19892,13 @@
         <v>0</v>
       </c>
       <c r="V191" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W191" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X191" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y191" s="9" t="n">
         <v>0</v>
@@ -19916,13 +19910,9 @@
         <v>1</v>
       </c>
       <c r="AB191" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC191" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -19932,19 +19922,19 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>5917</v>
+        <v>8693</v>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Chamber Toastmasters</t>
+          <t>Rochester Break Of Day Toastmasters Club</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>10</v>
@@ -19958,25 +19948,25 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J192" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L192" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L192" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M192" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N192" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O192" s="7" t="inlineStr">
@@ -19985,16 +19975,16 @@
         </is>
       </c>
       <c r="P192" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q192" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R192" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S192" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T192" s="10" t="n">
         <v>1</v>
@@ -20003,31 +19993,27 @@
         <v>0</v>
       </c>
       <c r="V192" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W192" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X192" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z192" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA192" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB192" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Y192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z192" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB192" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC192" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -20037,19 +20023,19 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>821458</v>
+        <v>7470</v>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Humor-US Club</t>
+          <t>Southern Minnesota Mentors Club</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F193" s="6" t="n">
         <v>10</v>
@@ -20063,13 +20049,13 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
@@ -20090,7 +20076,7 @@
         </is>
       </c>
       <c r="P193" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q193" s="9" t="n">
         <v>0</v>
@@ -20099,7 +20085,7 @@
         <v>0</v>
       </c>
       <c r="S193" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T193" s="9" t="n">
         <v>0</v>
@@ -20114,19 +20100,19 @@
         <v>0</v>
       </c>
       <c r="X193" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z193" s="10" t="n">
-        <v>1</v>
+      <c r="Z193" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA193" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB193" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC193" s="4" t="inlineStr"/>
     </row>
@@ -20138,15 +20124,15 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>1128511</v>
+        <v>2440926</v>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Lunchbunch Toastmasters</t>
+          <t>TNT- Toastmasters - N - Technology</t>
         </is>
       </c>
       <c r="E194" s="5" t="n">
@@ -20164,13 +20150,13 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J194" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
@@ -20194,13 +20180,13 @@
         <v>0</v>
       </c>
       <c r="Q194" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R194" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S194" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T194" s="9" t="n">
         <v>0</v>
@@ -20209,13 +20195,13 @@
         <v>0</v>
       </c>
       <c r="V194" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W194" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X194" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y194" s="9" t="n">
         <v>0</v>
@@ -20227,9 +20213,13 @@
         <v>1</v>
       </c>
       <c r="AB194" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC194" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC194" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -20243,15 +20233,15 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>1883</v>
+        <v>5917</v>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Rochester Suburban Club</t>
+          <t>Chamber Toastmasters</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F195" s="6" t="n">
         <v>10</v>
@@ -20265,25 +20255,25 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J195" s="4" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L195" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M195" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N195" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O195" s="7" t="inlineStr">
@@ -20292,10 +20282,10 @@
         </is>
       </c>
       <c r="P195" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q195" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R195" s="9" t="n">
         <v>0</v>
@@ -20303,34 +20293,38 @@
       <c r="S195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T195" s="9" t="n">
-        <v>0</v>
+      <c r="T195" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U195" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V195" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X195" s="9" t="n">
-        <v>2</v>
+      <c r="X195" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA195" s="10" t="n">
-        <v>1</v>
+      <c r="Z195" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA195" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB195" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC195" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC195" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -20344,11 +20338,11 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>6747</v>
+        <v>821458</v>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Rochester Technology Campus Toastmasters</t>
+          <t>Humor-US Club</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">
@@ -20366,13 +20360,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J196" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L196" s="7" t="inlineStr">
         <is>
@@ -20393,7 +20387,7 @@
         </is>
       </c>
       <c r="P196" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q196" s="9" t="n">
         <v>0</v>
@@ -20402,7 +20396,7 @@
         <v>0</v>
       </c>
       <c r="S196" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T196" s="9" t="n">
         <v>0</v>
@@ -20417,24 +20411,327 @@
         <v>0</v>
       </c>
       <c r="X196" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z196" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA196" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB196" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC196" s="4" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="n">
+        <v>1128511</v>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>Lunchbunch Toastmasters</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G197" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J197" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K197" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M197" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N197" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O197" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V197" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X197" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z197" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA197" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB197" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC197" s="4" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>Rochester Suburban Club</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G198" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z196" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA196" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB196" s="4" t="n">
+      <c r="J198" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K198" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L198" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M198" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N198" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O198" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P198" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q198" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R198" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T198" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V198" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W198" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X198" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AC196" s="4" t="inlineStr"/>
+      <c r="Y198" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z198" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA198" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB198" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC198" s="4" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="n">
+        <v>6747</v>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>Rochester Technology Campus Toastmasters</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G199" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H199" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I199" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J199" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K199" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M199" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N199" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O199" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P199" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q199" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R199" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T199" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V199" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W199" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X199" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y199" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z199" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA199" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB199" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC199" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC196"/>
+  <autoFilter ref="A1:AC199"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20668,7 +20965,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -20719,7 +21016,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -20752,7 +21049,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -20767,7 +21064,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -20833,7 +21130,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -20932,7 +21229,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -20965,7 +21262,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -20983,7 +21280,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -20998,7 +21295,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -21016,7 +21313,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -21031,7 +21328,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -21082,7 +21379,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -21097,7 +21394,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -21115,7 +21412,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -21130,7 +21427,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -21145,16 +21442,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -21163,7 +21460,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -21181,7 +21478,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -21196,7 +21493,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -21247,7 +21544,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -21262,7 +21559,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -21295,7 +21592,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -21346,7 +21643,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -21379,7 +21676,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -21460,7 +21757,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -21493,7 +21790,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -21508,16 +21805,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -21526,7 +21823,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -21541,16 +21838,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -21610,7 +21907,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -21625,7 +21922,7 @@
         <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -21658,7 +21955,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">

--- a/docs/d/06/inyear.xlsx
+++ b/docs/d/06/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/06/inyear.xlsx
+++ b/docs/d/06/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/06/inyear.xlsx
+++ b/docs/d/06/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/06/inyear.xlsx
+++ b/docs/d/06/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/06/inyear.xlsx
+++ b/docs/d/06/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 43 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 43 clubs short</t>
         </is>
       </c>
     </row>
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -4048,13 +4048,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4543,13 +4543,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4642,13 +4642,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -5242,13 +5242,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -6034,13 +6034,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6236,13 +6236,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6935,13 +6935,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="S67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="10" t="n">
         <v>1</v>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -8129,13 +8129,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="P75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="9" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9273,8 +9273,8 @@
       <c r="R86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S86" s="9" t="n">
-        <v>1</v>
+      <c r="S86" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T86" s="10" t="n">
         <v>1</v>
@@ -10155,13 +10155,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10462,13 +10462,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10870,13 +10870,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -11072,13 +11072,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11987,17 +11987,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L113" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -12492,17 +12492,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L118" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12537,7 +12537,7 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12791,13 +12791,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12829,14 +12829,14 @@
       <c r="S121" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T121" s="9" t="n">
-        <v>0</v>
+      <c r="T121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
@@ -13412,7 +13412,7 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q127" s="9" t="n">
         <v>0</v>
@@ -13781,13 +13781,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14280,13 +14280,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14324,8 +14324,8 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="9" t="n">
-        <v>2</v>
+      <c r="V136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -14676,13 +14676,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
@@ -14973,13 +14973,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15272,13 +15272,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -15882,13 +15882,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -16290,13 +16290,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>0</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -16789,7 +16789,7 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -16841,8 +16841,8 @@
       <c r="S161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T161" s="9" t="n">
-        <v>0</v>
+      <c r="T161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U161" s="9" t="n">
         <v>0</v>
@@ -16908,13 +16908,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -17514,13 +17514,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -17720,13 +17720,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -17821,13 +17821,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>0</v>
       </c>
       <c r="V171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W171" s="9" t="n">
         <v>0</v>
@@ -18124,13 +18124,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>0</v>
       </c>
       <c r="V174" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W174" s="9" t="n">
         <v>0</v>
@@ -18516,7 +18516,7 @@
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -18571,8 +18571,8 @@
       <c r="T178" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U178" s="9" t="n">
-        <v>0</v>
+      <c r="U178" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V178" s="9" t="n">
         <v>0</v>
@@ -19120,7 +19120,7 @@
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19172,8 +19172,8 @@
       <c r="S184" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T184" s="9" t="n">
-        <v>0</v>
+      <c r="T184" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U184" s="9" t="n">
         <v>0</v>
@@ -19338,13 +19338,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
@@ -19443,13 +19443,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
@@ -20150,13 +20150,13 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -21460,7 +21460,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -21493,7 +21493,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -21511,7 +21511,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -21610,7 +21610,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -21841,7 +21841,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -21874,7 +21874,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/06/inyear.xlsx
+++ b/docs/d/06/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 43 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 43 clubs short</t>
         </is>
       </c>
     </row>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1912,8 +1912,8 @@
       <c r="W12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X12" s="9" t="n">
-        <v>3</v>
+      <c r="X12" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="9" t="n">
         <v>0</v>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -2760,10 +2760,10 @@
         <v>9</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3097,14 +3097,14 @@
       <c r="T24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U24" s="9" t="n">
-        <v>0</v>
+      <c r="U24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V24" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>6</v>
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3155,13 +3155,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>0</v>
@@ -3193,8 +3193,8 @@
       <c r="S25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T25" s="9" t="n">
-        <v>0</v>
+      <c r="T25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U25" s="9" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -3751,13 +3751,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4878,8 +4878,8 @@
       <c r="S42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="9" t="n">
-        <v>0</v>
+      <c r="T42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U42" s="9" t="n">
         <v>0</v>
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -6034,13 +6034,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6236,13 +6236,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6387,8 +6387,8 @@
       <c r="W57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X57" s="9" t="n">
-        <v>2</v>
+      <c r="X57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y57" s="9" t="n">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6935,13 +6935,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -8234,13 +8234,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" s="9" t="n">
         <v>0</v>
@@ -9541,17 +9541,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9586,7 +9586,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9646,13 +9646,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="Q90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
@@ -9691,7 +9691,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q98" s="9" t="n">
         <v>0</v>
@@ -10549,7 +10549,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10563,13 +10563,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10607,8 +10607,8 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="9" t="n">
-        <v>2</v>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -13088,13 +13088,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q128" s="9" t="n">
         <v>0</v>
@@ -13781,13 +13781,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14676,13 +14676,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -14817,7 +14817,7 @@
         <v>1</v>
       </c>
       <c r="U141" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V141" s="9" t="n">
         <v>0</v>
@@ -15024,7 +15024,7 @@
         <v>0</v>
       </c>
       <c r="X143" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
@@ -15272,13 +15272,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15373,13 +15373,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15610,8 +15610,8 @@
       <c r="R149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S149" s="9" t="n">
-        <v>1</v>
+      <c r="S149" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T149" s="9" t="n">
         <v>0</v>
@@ -16216,7 +16216,7 @@
         </is>
       </c>
       <c r="P155" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q155" s="9" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16627,7 +16627,7 @@
         <v>2</v>
       </c>
       <c r="Q159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R159" s="9" t="n">
         <v>0</v>
@@ -16635,8 +16635,8 @@
       <c r="S159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T159" s="9" t="n">
-        <v>0</v>
+      <c r="T159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U159" s="9" t="n">
         <v>0</v>
@@ -17821,13 +17821,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
@@ -18124,13 +18124,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>0</v>
       </c>
       <c r="V174" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W174" s="9" t="n">
         <v>0</v>
@@ -18629,13 +18629,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>0</v>
       </c>
       <c r="V179" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W179" s="9" t="n">
         <v>0</v>
@@ -18918,7 +18918,7 @@
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>10</v>
@@ -18961,8 +18961,8 @@
       <c r="P182" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q182" s="9" t="n">
-        <v>1</v>
+      <c r="Q182" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R182" s="9" t="n">
         <v>0</v>
@@ -19263,7 +19263,7 @@
         <v>0</v>
       </c>
       <c r="Q185" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R185" s="9" t="n">
         <v>0</v>
@@ -19443,13 +19443,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>0</v>
       </c>
       <c r="V187" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W187" s="9" t="n">
         <v>0</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>10</v>
@@ -20188,8 +20188,8 @@
       <c r="S194" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T194" s="9" t="n">
-        <v>0</v>
+      <c r="T194" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U194" s="9" t="n">
         <v>0</v>
@@ -20291,7 +20291,7 @@
         <v>0</v>
       </c>
       <c r="S195" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T195" s="10" t="n">
         <v>1</v>
@@ -20950,7 +20950,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -21049,7 +21049,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -21328,7 +21328,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -21379,7 +21379,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -21676,7 +21676,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -21874,7 +21874,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -21940,7 +21940,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
